--- a/output/graficos_nacionales/plot_nacional_serie_s_isapre_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_s_isapre_a_2021.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:21</t>
+    <t xml:space="preserve">2026-09-09 21:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_s_isapre_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_s_isapre_a_2021.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:08</t>
+    <t xml:space="preserve">2026-09-16 20:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_s_isapre_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_s_isapre_a_2021.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-16 20:47</t>
+    <t xml:space="preserve">2026-09-25 10:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_s_isapre_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_s_isapre_a_2021.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 10:53</t>
+    <t xml:space="preserve">2026-09-25 17:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_s_isapre_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_s_isapre_a_2021.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 17:20</t>
+    <t xml:space="preserve">2026-10-05 19:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
